--- a/betting_lines_open_2026.xlsx
+++ b/betting_lines_open_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\OneDrive - Hunter - CUNY\Documents\Football-DNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7116C22-0578-441F-971C-FBEEBA9A4EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE96F25-9EEB-4815-9552-0F36EB6C92EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{38E66C5D-58C4-4402-8F4D-2FF7B602BD04}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{38E66C5D-58C4-4402-8F4D-2FF7B602BD04}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 11" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>game</t>
   </si>
@@ -148,6 +148,54 @@
   </si>
   <si>
     <t>NYG_LA</t>
+  </si>
+  <si>
+    <t>ATL_GB</t>
+  </si>
+  <si>
+    <t>SEA_WAS</t>
+  </si>
+  <si>
+    <t>CIN_PIT</t>
+  </si>
+  <si>
+    <t>NYJ_DET</t>
+  </si>
+  <si>
+    <t>TEN_NYG</t>
+  </si>
+  <si>
+    <t>NE_JAX</t>
+  </si>
+  <si>
+    <t>KC_MIA</t>
+  </si>
+  <si>
+    <t>HOU_IND</t>
+  </si>
+  <si>
+    <t>CAR_CLE</t>
+  </si>
+  <si>
+    <t>LAC_BUF</t>
+  </si>
+  <si>
+    <t>MIN_TB</t>
+  </si>
+  <si>
+    <t>ARI_SF</t>
+  </si>
+  <si>
+    <t>LV_NO</t>
+  </si>
+  <si>
+    <t>BAL_DAL</t>
+  </si>
+  <si>
+    <t>LA_DEN</t>
+  </si>
+  <si>
+    <t>PHI_CHI</t>
   </si>
 </sst>
 </file>
@@ -705,7 +753,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD36202-D83D-42C3-9E22-D680F63FC59E}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -946,6 +994,230 @@
         <v>8.5</v>
       </c>
     </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18">
+        <v>46.5</v>
+      </c>
+      <c r="D18">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19">
+        <v>46.5</v>
+      </c>
+      <c r="D19">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20">
+        <v>47.5</v>
+      </c>
+      <c r="D20">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21">
+        <v>45.5</v>
+      </c>
+      <c r="D21">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22">
+        <v>45.5</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23">
+        <v>45.5</v>
+      </c>
+      <c r="D23">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24">
+        <v>44.5</v>
+      </c>
+      <c r="D24">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25">
+        <v>45.5</v>
+      </c>
+      <c r="D25">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>3</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26">
+        <v>39.5</v>
+      </c>
+      <c r="D26">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27">
+        <v>48.5</v>
+      </c>
+      <c r="D27">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28">
+        <v>44.5</v>
+      </c>
+      <c r="D28">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29">
+        <v>46.5</v>
+      </c>
+      <c r="D29">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30">
+        <v>42.5</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31">
+        <v>50.5</v>
+      </c>
+      <c r="D31">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32">
+        <v>45.5</v>
+      </c>
+      <c r="D32">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33">
+        <v>46.5</v>
+      </c>
+      <c r="D33">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/betting_lines_open_2026.xlsx
+++ b/betting_lines_open_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\OneDrive - Hunter - CUNY\Documents\Football-DNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE96F25-9EEB-4815-9552-0F36EB6C92EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3990ED3B-32D8-44FE-9BBD-59DD11E831F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{38E66C5D-58C4-4402-8F4D-2FF7B602BD04}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <t>game</t>
   </si>
@@ -196,6 +196,54 @@
   </si>
   <si>
     <t>PHI_CHI</t>
+  </si>
+  <si>
+    <t>PIT_CLE</t>
+  </si>
+  <si>
+    <t>IND_WAS</t>
+  </si>
+  <si>
+    <t>NE_BUF</t>
+  </si>
+  <si>
+    <t>NYJ_CHI</t>
+  </si>
+  <si>
+    <t>ARI_NYG</t>
+  </si>
+  <si>
+    <t>DAL_HOU</t>
+  </si>
+  <si>
+    <t>JAX_CIN</t>
+  </si>
+  <si>
+    <t>GB_TB</t>
+  </si>
+  <si>
+    <t>LA_PHI</t>
+  </si>
+  <si>
+    <t>TEN_BAL</t>
+  </si>
+  <si>
+    <t>MIA_MIN</t>
+  </si>
+  <si>
+    <t>DEN_SF</t>
+  </si>
+  <si>
+    <t>KC_LV</t>
+  </si>
+  <si>
+    <t>LAC_SEA</t>
+  </si>
+  <si>
+    <t>DET_CAR</t>
+  </si>
+  <si>
+    <t>ATL_NO</t>
   </si>
 </sst>
 </file>
@@ -753,7 +801,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD36202-D83D-42C3-9E22-D680F63FC59E}">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -1218,6 +1266,230 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34">
+        <v>40.5</v>
+      </c>
+      <c r="D34">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35">
+        <v>48.5</v>
+      </c>
+      <c r="D35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36">
+        <v>49.5</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37">
+        <v>45.5</v>
+      </c>
+      <c r="D37">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38">
+        <v>45.5</v>
+      </c>
+      <c r="D38">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39">
+        <v>47.5</v>
+      </c>
+      <c r="D39">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40">
+        <v>51.5</v>
+      </c>
+      <c r="D40">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41">
+        <v>47.5</v>
+      </c>
+      <c r="D41">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42">
+        <v>47.5</v>
+      </c>
+      <c r="D42">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43">
+        <v>47.5</v>
+      </c>
+      <c r="D43">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44">
+        <v>43.5</v>
+      </c>
+      <c r="D44">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>64</v>
+      </c>
+      <c r="C45">
+        <v>46.5</v>
+      </c>
+      <c r="D45">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46">
+        <v>43.5</v>
+      </c>
+      <c r="D46">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>4</v>
+      </c>
+      <c r="B47" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47">
+        <v>45.5</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48">
+        <v>47.5</v>
+      </c>
+      <c r="D48">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>4</v>
+      </c>
+      <c r="B49" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49">
+        <v>45.5</v>
+      </c>
+      <c r="D49">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/betting_lines_open_2026.xlsx
+++ b/betting_lines_open_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\OneDrive - Hunter - CUNY\Documents\Football-DNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3990ED3B-32D8-44FE-9BBD-59DD11E831F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290EF09A-FA49-450A-AA1D-4C95A86AFC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{38E66C5D-58C4-4402-8F4D-2FF7B602BD04}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="84">
   <si>
     <t>game</t>
   </si>
@@ -244,6 +244,51 @@
   </si>
   <si>
     <t>ATL_NO</t>
+  </si>
+  <si>
+    <t>TB_DAL</t>
+  </si>
+  <si>
+    <t>PHI_JAX</t>
+  </si>
+  <si>
+    <t>IND_PIT</t>
+  </si>
+  <si>
+    <t>MIN_NO</t>
+  </si>
+  <si>
+    <t>CLE_NYJ</t>
+  </si>
+  <si>
+    <t>CIN_MIA</t>
+  </si>
+  <si>
+    <t>LV_NE</t>
+  </si>
+  <si>
+    <t>NYG_WAS</t>
+  </si>
+  <si>
+    <t>HOU_TEN</t>
+  </si>
+  <si>
+    <t>CHI_GB</t>
+  </si>
+  <si>
+    <t>DEN_LAC</t>
+  </si>
+  <si>
+    <t>SF_SEA</t>
+  </si>
+  <si>
+    <t>DET_ARI</t>
+  </si>
+  <si>
+    <t>BAL_ATL</t>
+  </si>
+  <si>
+    <t>BUF_LA</t>
   </si>
 </sst>
 </file>
@@ -801,7 +846,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD36202-D83D-42C3-9E22-D680F63FC59E}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -1490,6 +1535,216 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50">
+        <v>52.5</v>
+      </c>
+      <c r="D50">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51">
+        <v>43.5</v>
+      </c>
+      <c r="D51">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52">
+        <v>47.5</v>
+      </c>
+      <c r="D52">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53">
+        <v>44.5</v>
+      </c>
+      <c r="D53">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54">
+        <v>39.5</v>
+      </c>
+      <c r="D54">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55">
+        <v>49.5</v>
+      </c>
+      <c r="D55">
+        <v>-8.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56">
+        <v>44.5</v>
+      </c>
+      <c r="D56">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57">
+        <v>48.5</v>
+      </c>
+      <c r="D57">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>5</v>
+      </c>
+      <c r="B58" t="s">
+        <v>77</v>
+      </c>
+      <c r="C58">
+        <v>43.5</v>
+      </c>
+      <c r="D58">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>5</v>
+      </c>
+      <c r="B59" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59">
+        <v>49.5</v>
+      </c>
+      <c r="D59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60">
+        <v>44.5</v>
+      </c>
+      <c r="D60">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>5</v>
+      </c>
+      <c r="B61" t="s">
+        <v>80</v>
+      </c>
+      <c r="C61">
+        <v>48.5</v>
+      </c>
+      <c r="D61">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>5</v>
+      </c>
+      <c r="B62" t="s">
+        <v>81</v>
+      </c>
+      <c r="C62">
+        <v>49.5</v>
+      </c>
+      <c r="D62">
+        <v>-8.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="B63" t="s">
+        <v>82</v>
+      </c>
+      <c r="C63">
+        <v>48.5</v>
+      </c>
+      <c r="D63">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64">
+        <v>53.5</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/betting_lines_open_2026.xlsx
+++ b/betting_lines_open_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\OneDrive - Hunter - CUNY\Documents\Football-DNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290EF09A-FA49-450A-AA1D-4C95A86AFC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0264E3A-CC1D-4478-8803-563321D1F0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{38E66C5D-58C4-4402-8F4D-2FF7B602BD04}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{38E66C5D-58C4-4402-8F4D-2FF7B602BD04}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 11" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="98">
   <si>
     <t>game</t>
   </si>
@@ -289,6 +289,48 @@
   </si>
   <si>
     <t>BUF_LA</t>
+  </si>
+  <si>
+    <t>SEA_DEN</t>
+  </si>
+  <si>
+    <t>HOU_JAX</t>
+  </si>
+  <si>
+    <t>NYJ_NE</t>
+  </si>
+  <si>
+    <t>PIT_TB</t>
+  </si>
+  <si>
+    <t>BAL_CLE</t>
+  </si>
+  <si>
+    <t>CHI_ATL</t>
+  </si>
+  <si>
+    <t>TEN_IND</t>
+  </si>
+  <si>
+    <t>CAR_PHI</t>
+  </si>
+  <si>
+    <t>NO_NYG</t>
+  </si>
+  <si>
+    <t>ARI_LA</t>
+  </si>
+  <si>
+    <t>BUF_LV</t>
+  </si>
+  <si>
+    <t>LAC_KC</t>
+  </si>
+  <si>
+    <t>DAL_GB</t>
+  </si>
+  <si>
+    <t>WAS_SF</t>
   </si>
 </sst>
 </file>
@@ -846,7 +888,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD36202-D83D-42C3-9E22-D680F63FC59E}">
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -1745,6 +1787,202 @@
         <v>3</v>
       </c>
     </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>6</v>
+      </c>
+      <c r="B65" t="s">
+        <v>84</v>
+      </c>
+      <c r="C65">
+        <v>43.5</v>
+      </c>
+      <c r="D65">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>6</v>
+      </c>
+      <c r="B66" t="s">
+        <v>85</v>
+      </c>
+      <c r="C66">
+        <v>41.5</v>
+      </c>
+      <c r="D66">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>6</v>
+      </c>
+      <c r="B67" t="s">
+        <v>86</v>
+      </c>
+      <c r="C67">
+        <v>42.5</v>
+      </c>
+      <c r="D67">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>6</v>
+      </c>
+      <c r="B68" t="s">
+        <v>87</v>
+      </c>
+      <c r="C68">
+        <v>45.5</v>
+      </c>
+      <c r="D68">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>6</v>
+      </c>
+      <c r="B69" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69">
+        <v>44.5</v>
+      </c>
+      <c r="D69">
+        <v>-6.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>6</v>
+      </c>
+      <c r="B70" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70">
+        <v>47.5</v>
+      </c>
+      <c r="D70">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>6</v>
+      </c>
+      <c r="B71" t="s">
+        <v>90</v>
+      </c>
+      <c r="C71">
+        <v>48.5</v>
+      </c>
+      <c r="D71">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>6</v>
+      </c>
+      <c r="B72" t="s">
+        <v>91</v>
+      </c>
+      <c r="C72">
+        <v>43.5</v>
+      </c>
+      <c r="D72">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>6</v>
+      </c>
+      <c r="B73" t="s">
+        <v>92</v>
+      </c>
+      <c r="C73">
+        <v>45.5</v>
+      </c>
+      <c r="D73">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>6</v>
+      </c>
+      <c r="B74" t="s">
+        <v>93</v>
+      </c>
+      <c r="C74">
+        <v>47.5</v>
+      </c>
+      <c r="D74">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>6</v>
+      </c>
+      <c r="B75" t="s">
+        <v>94</v>
+      </c>
+      <c r="C75">
+        <v>47.5</v>
+      </c>
+      <c r="D75">
+        <v>-6.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>6</v>
+      </c>
+      <c r="B76" t="s">
+        <v>95</v>
+      </c>
+      <c r="C76">
+        <v>46.5</v>
+      </c>
+      <c r="D76">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>6</v>
+      </c>
+      <c r="B77" t="s">
+        <v>96</v>
+      </c>
+      <c r="C77">
+        <v>51.5</v>
+      </c>
+      <c r="D77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>6</v>
+      </c>
+      <c r="B78" t="s">
+        <v>97</v>
+      </c>
+      <c r="C78">
+        <v>50.5</v>
+      </c>
+      <c r="D78">
+        <v>5.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/betting_lines_open_2026.xlsx
+++ b/betting_lines_open_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\OneDrive - Hunter - CUNY\Documents\Football-DNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0264E3A-CC1D-4478-8803-563321D1F0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112618E5-F664-4CB6-84F3-9C4CB9F3BC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{38E66C5D-58C4-4402-8F4D-2FF7B602BD04}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{38E66C5D-58C4-4402-8F4D-2FF7B602BD04}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 11" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="112">
   <si>
     <t>game</t>
   </si>
@@ -331,6 +331,48 @@
   </si>
   <si>
     <t>WAS_SF</t>
+  </si>
+  <si>
+    <t>NE_CHI</t>
+  </si>
+  <si>
+    <t>PIT_NO</t>
+  </si>
+  <si>
+    <t>TB_CAR</t>
+  </si>
+  <si>
+    <t>MIA_NYJ</t>
+  </si>
+  <si>
+    <t>CLE_TEN</t>
+  </si>
+  <si>
+    <t>NYG_HOU</t>
+  </si>
+  <si>
+    <t>SF_ATL</t>
+  </si>
+  <si>
+    <t>IND_MIN</t>
+  </si>
+  <si>
+    <t>CIN_BAL</t>
+  </si>
+  <si>
+    <t>DEN_ARI</t>
+  </si>
+  <si>
+    <t>GB_DET</t>
+  </si>
+  <si>
+    <t>LA_LV</t>
+  </si>
+  <si>
+    <t>KC_SEA</t>
+  </si>
+  <si>
+    <t>DAL_PHI</t>
   </si>
 </sst>
 </file>
@@ -888,7 +930,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD36202-D83D-42C3-9E22-D680F63FC59E}">
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -1983,6 +2025,202 @@
         <v>5.5</v>
       </c>
     </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>98</v>
+      </c>
+      <c r="C79">
+        <v>47.5</v>
+      </c>
+      <c r="D79">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>7</v>
+      </c>
+      <c r="B80" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80">
+        <v>42.5</v>
+      </c>
+      <c r="D80">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>7</v>
+      </c>
+      <c r="B81" t="s">
+        <v>100</v>
+      </c>
+      <c r="C81">
+        <v>45.5</v>
+      </c>
+      <c r="D81">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>7</v>
+      </c>
+      <c r="B82" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82">
+        <v>41.5</v>
+      </c>
+      <c r="D82">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>7</v>
+      </c>
+      <c r="B83" t="s">
+        <v>102</v>
+      </c>
+      <c r="C83">
+        <v>40.5</v>
+      </c>
+      <c r="D83">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>7</v>
+      </c>
+      <c r="B84" t="s">
+        <v>103</v>
+      </c>
+      <c r="C84">
+        <v>43.5</v>
+      </c>
+      <c r="D84">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>7</v>
+      </c>
+      <c r="B85" t="s">
+        <v>104</v>
+      </c>
+      <c r="C85">
+        <v>47.5</v>
+      </c>
+      <c r="D85">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>7</v>
+      </c>
+      <c r="B86" t="s">
+        <v>105</v>
+      </c>
+      <c r="C86">
+        <v>47.5</v>
+      </c>
+      <c r="D86">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>7</v>
+      </c>
+      <c r="B87" t="s">
+        <v>106</v>
+      </c>
+      <c r="C87">
+        <v>52.5</v>
+      </c>
+      <c r="D87">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>7</v>
+      </c>
+      <c r="B88" t="s">
+        <v>107</v>
+      </c>
+      <c r="C88">
+        <v>43.5</v>
+      </c>
+      <c r="D88">
+        <v>-7.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>7</v>
+      </c>
+      <c r="B89" t="s">
+        <v>108</v>
+      </c>
+      <c r="C89">
+        <v>50.5</v>
+      </c>
+      <c r="D89">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>7</v>
+      </c>
+      <c r="B90" t="s">
+        <v>109</v>
+      </c>
+      <c r="C90">
+        <v>46.5</v>
+      </c>
+      <c r="D90">
+        <v>-7.5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>7</v>
+      </c>
+      <c r="B91" t="s">
+        <v>110</v>
+      </c>
+      <c r="C91">
+        <v>45.5</v>
+      </c>
+      <c r="D91">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>7</v>
+      </c>
+      <c r="B92" t="s">
+        <v>111</v>
+      </c>
+      <c r="C92">
+        <v>48.5</v>
+      </c>
+      <c r="D92">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/betting_lines_open_2026.xlsx
+++ b/betting_lines_open_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\OneDrive - Hunter - CUNY\Documents\Football-DNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{112618E5-F664-4CB6-84F3-9C4CB9F3BC42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FD80DF-EA47-402A-AAEE-FA4D938E24B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{38E66C5D-58C4-4402-8F4D-2FF7B602BD04}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="126">
   <si>
     <t>game</t>
   </si>
@@ -373,6 +373,48 @@
   </si>
   <si>
     <t>DAL_PHI</t>
+  </si>
+  <si>
+    <t>CAR_GB</t>
+  </si>
+  <si>
+    <t>MIN_DET</t>
+  </si>
+  <si>
+    <t>LV_NYJ</t>
+  </si>
+  <si>
+    <t>ARI_DAL</t>
+  </si>
+  <si>
+    <t>ATL_TB</t>
+  </si>
+  <si>
+    <t>BAL_BUF</t>
+  </si>
+  <si>
+    <t>IND_JAX</t>
+  </si>
+  <si>
+    <t>TEN_CIN</t>
+  </si>
+  <si>
+    <t>CLE_PIT</t>
+  </si>
+  <si>
+    <t>LAC_LA</t>
+  </si>
+  <si>
+    <t>KC_DEN</t>
+  </si>
+  <si>
+    <t>NE_MIA</t>
+  </si>
+  <si>
+    <t>PHI_WAS</t>
+  </si>
+  <si>
+    <t>CHI_SEA</t>
   </si>
 </sst>
 </file>
@@ -930,7 +972,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FD36202-D83D-42C3-9E22-D680F63FC59E}">
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -2221,6 +2263,202 @@
         <v>3</v>
       </c>
     </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>8</v>
+      </c>
+      <c r="B93" t="s">
+        <v>112</v>
+      </c>
+      <c r="C93">
+        <v>45.5</v>
+      </c>
+      <c r="D93">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>8</v>
+      </c>
+      <c r="B94" t="s">
+        <v>113</v>
+      </c>
+      <c r="C94">
+        <v>47.5</v>
+      </c>
+      <c r="D94">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>8</v>
+      </c>
+      <c r="B95" t="s">
+        <v>114</v>
+      </c>
+      <c r="C95">
+        <v>41.5</v>
+      </c>
+      <c r="D95">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>8</v>
+      </c>
+      <c r="B96" t="s">
+        <v>115</v>
+      </c>
+      <c r="C96">
+        <v>49.5</v>
+      </c>
+      <c r="D96">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>8</v>
+      </c>
+      <c r="B97" t="s">
+        <v>116</v>
+      </c>
+      <c r="C97">
+        <v>46.5</v>
+      </c>
+      <c r="D97">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>8</v>
+      </c>
+      <c r="B98" t="s">
+        <v>117</v>
+      </c>
+      <c r="C98">
+        <v>51.5</v>
+      </c>
+      <c r="D98">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>8</v>
+      </c>
+      <c r="B99" t="s">
+        <v>118</v>
+      </c>
+      <c r="C99">
+        <v>49.5</v>
+      </c>
+      <c r="D99">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>8</v>
+      </c>
+      <c r="B100" t="s">
+        <v>119</v>
+      </c>
+      <c r="C100">
+        <v>49.5</v>
+      </c>
+      <c r="D100">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>8</v>
+      </c>
+      <c r="B101" t="s">
+        <v>120</v>
+      </c>
+      <c r="C101">
+        <v>39.5</v>
+      </c>
+      <c r="D101">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>8</v>
+      </c>
+      <c r="B102" t="s">
+        <v>121</v>
+      </c>
+      <c r="C102">
+        <v>48.5</v>
+      </c>
+      <c r="D102">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>8</v>
+      </c>
+      <c r="B103" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103">
+        <v>43.5</v>
+      </c>
+      <c r="D103">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>8</v>
+      </c>
+      <c r="B104" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104">
+        <v>45.5</v>
+      </c>
+      <c r="D104">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>8</v>
+      </c>
+      <c r="B105" t="s">
+        <v>124</v>
+      </c>
+      <c r="C105">
+        <v>46.5</v>
+      </c>
+      <c r="D105">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>8</v>
+      </c>
+      <c r="B106" t="s">
+        <v>125</v>
+      </c>
+      <c r="C106">
+        <v>47.5</v>
+      </c>
+      <c r="D106">
+        <v>4.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
